--- a/1-运维服务目录/0102-组织级运维服务目录.xlsx
+++ b/1-运维服务目录/0102-组织级运维服务目录.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9575" tabRatio="954" firstSheet="1"/>
+    <workbookView windowWidth="22188" windowHeight="9575" tabRatio="954" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="服务目录" sheetId="8" r:id="rId1"/>
@@ -491,7 +491,7 @@
     <t>对故障进行定位并解决或提供相关技术支持，以保证客户业务正常运行</t>
   </si>
   <si>
-    <t xml:space="preserve">公共机构能源管理云平台系统 、公共机构垃圾分类计重管理云平台系统 、水节约型机关信息化管理系统等自研的应用软件； </t>
+    <t>枣安低空智控一体化平台；蒙阴两山智慧城市综合管理平台；烟台田园综合体智慧农业管理系统；</t>
   </si>
   <si>
     <t>1、对业务数据进行维护、更新；</t>
@@ -528,7 +528,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -575,13 +575,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1108,7 +1101,7 @@
     </border>
   </borders>
   <cellStyleXfs count="55">
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
@@ -1117,54 +1110,54 @@
     <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="8" applyNumberFormat="0" applyFont="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="11" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="12" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="11" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="13" applyNumberFormat="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="11" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="12" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="11" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="13" applyNumberFormat="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="44" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="42" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="41" fontId="24" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="41" fontId="23" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
@@ -2619,7 +2612,7 @@
       </c>
       <c r="B8" s="2"/>
     </row>
-    <row r="9" ht="30" customHeight="1" spans="1:2">
+    <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
